--- a/Data/Home/BedroomOne.UltravioletLevel.xlsx
+++ b/Data/Home/BedroomOne.UltravioletLevel.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709428778</v>
+        <v>1712116227</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709428799</v>
+        <v>1712116243</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709428829</v>
+        <v>1712116261</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709428855</v>
+        <v>1712116282</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +601,15 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: Moderate</t>
+          <t>BedroomOne.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +628,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709429270</v>
+        <v>1712116313</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +642,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +661,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709438114</v>
+        <v>1712121177</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -657,10 +671,15 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: Moderate</t>
+          <t>BedroomOne.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +698,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709444618</v>
+        <v>1712126336</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -689,10 +708,11 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +731,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709445829</v>
+        <v>1712135300</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -721,10 +741,11 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomOne.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +764,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709688498</v>
+        <v>1712137161</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +778,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +797,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709688523</v>
+        <v>1712137986</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -785,10 +807,11 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: Moderate</t>
+          <t>BedroomOne.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +830,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709688552</v>
+        <v>1712466941</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -817,10 +840,11 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomOne.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +863,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709688578</v>
+        <v>1712466951</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -849,10 +873,11 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomOne.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +896,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709688640</v>
+        <v>1712466964</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +910,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709693175</v>
+        <v>1712467792</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +943,11 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +966,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709697541</v>
+        <v>1712473272</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +980,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +999,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709705365</v>
+        <v>1712483159</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1013,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1032,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709706733</v>
+        <v>1712485183</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1046,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1065,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709707367</v>
+        <v>1712486210</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1079,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1098,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1710034285</v>
+        <v>1713153832</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1112,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1131,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1710034314</v>
+        <v>1713153861</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1145,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1164,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1710034341</v>
+        <v>1713154110</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1178,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1197,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1710034372</v>
+        <v>1713165419</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1169,10 +1207,11 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomOne.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1230,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1710034451</v>
+        <v>1713172260</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1201,10 +1240,11 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomOne.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1263,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1710036839</v>
+        <v>1713173825</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1233,10 +1273,11 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomOne.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1296,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1710041135</v>
+        <v>1713844012</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1265,10 +1306,11 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomOne.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1329,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1710049018</v>
+        <v>1713844029</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1343,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1362,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1710050872</v>
+        <v>1713844047</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1329,10 +1372,11 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1395,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1710051667</v>
+        <v>1713844065</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1361,10 +1405,15 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomOne.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1432,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1710380321</v>
+        <v>1713844111</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1393,10 +1442,11 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1465,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1710380348</v>
+        <v>1713848172</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1425,10 +1475,15 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: Moderate</t>
+          <t>BedroomOne.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1502,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1710380381</v>
+        <v>1713854567</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1516,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1535,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1710380406</v>
+        <v>1713863631</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1545,11 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomOne.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1568,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1710380465</v>
+        <v>1713866029</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1521,10 +1578,11 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomOne.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1601,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1710384246</v>
+        <v>1713866878</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1553,10 +1611,11 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomOne.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1634,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1710388387</v>
+        <v>1714017408</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1585,10 +1644,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomOne.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1667,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1710395624</v>
+        <v>1714017436</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1681,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1700,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1710398123</v>
+        <v>1714018087</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1649,10 +1710,11 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1733,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1710398989</v>
+        <v>1714028999</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1681,10 +1743,11 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomOne.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1766,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1710551661</v>
+        <v>1714036201</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1780,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1799,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1710551696</v>
+        <v>1714037547</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1745,778 +1809,11 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>BedroomOne.UltravioletLevel.state: Moderate</t>
+          <t>BedroomOne.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>1710552136</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>1710559914</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>1710565228</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>1710566306</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: ExcessivelyLow</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>1710726852</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>1710726880</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>1710726911</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>1710726939</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: ExcessivelyHigh</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>1710727021</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>1710731769</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: ExcessivelyHigh</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>1710737046</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>1710745097</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>1710746529</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>1710747156</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: ExcessivelyLow</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>1710988009</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>1710988039</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>1710988065</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>1710988093</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: ExcessivelyHigh</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>1710988188</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>1710989547</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: ExcessivelyHigh</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>1710993947</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>1711001321</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>1711002960</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>BedroomOne</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>1711003777</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>BedroomOne.UltravioletLevel.state: ExcessivelyLow</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
